--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N91_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.37462352406056</v>
+        <v>2.985876322659842</v>
       </c>
       <c r="D2" t="n">
-        <v>18.12796725749638</v>
+        <v>2.945794679343161</v>
       </c>
       <c r="E2" t="n">
-        <v>12.7744340327532</v>
+        <v>2.075845530322395</v>
       </c>
       <c r="F2" t="n">
-        <v>12.25642961211501</v>
+        <v>1.991669811968689</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.97136173377567</v>
+        <v>3.407846281738546</v>
       </c>
       <c r="D3" t="n">
-        <v>22.16307825365909</v>
+        <v>3.601500216219602</v>
       </c>
       <c r="E3" t="n">
-        <v>12.7744340327532</v>
+        <v>2.075845530322395</v>
       </c>
       <c r="F3" t="n">
-        <v>12.25642961211501</v>
+        <v>1.991669811968689</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.67818573802008</v>
+        <v>7.585205182428263</v>
       </c>
       <c r="D4" t="n">
-        <v>45.90942599638673</v>
+        <v>7.460281724412844</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7744340327532</v>
+        <v>2.075845530322395</v>
       </c>
       <c r="F4" t="n">
-        <v>12.25642961211501</v>
+        <v>1.991669811968689</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
